--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_map_mark/lang_map_mark__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_map_mark/lang_map_mark__ui__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Pioneer Association</t>
+          <t>Hiệp Hội Tiên Phong</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Hẻm Núi Linh Hồn</t>
+          <t>Gorges of Spirits</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Đồng bằng Trung tâm</t>
+          <t>Central Plains</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Cao nguyên Desorock</t>
+          <t>Desorock Highland</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Bãi Lầy Whining Aix</t>
+          <t>Whining Aix's Mire</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Rừng Tối</t>
+          <t>Dim Forest</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Ma Anh ấy's Grocers</t>
+          <t>Cửa Hàng Ma He</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Interference Exchange</t>
+          <t>Trao Đổi Interference</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Một Sinh Vật Đột Biến đáng gờm nằm sâu trong Rừng Mờ. Thủ lĩnh của bọn Hoochief.</t>
+          <t>Một Sinh Vật Đột Biến đáng gờm nằm sâu trong Dim Forest. Thủ lĩnh của bọn Hoochief.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Discord thường hoạt động trong các khu mỏ và vùng núi, kích thước nhỏ, mức độ nguy hiểm tương đối thấp.</t>
+          <t>Tacet Discord thường hoạt động trong các khu mỏ và vùng núi, kích thước nhỏ, mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Discord này có hình dạng giống người, phân bố rộng rãi. Các đòn tấn công chủ yếu ở tầm gần và rất nguy hiểm.</t>
+          <t>Tacet Discord này có hình dạng giống người, phân bố rộng rãi. Các đòn tấn công chủ yếu ở tầm gần và rất nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Một Discord hình người có phạm vi phân bố rộng, chủ yếu tấn công tầm gần. Có chi trên đặc trưng một bên, tiềm ẩn một số rủi ro.</t>
+          <t>Một Tacet Discord hình người có phạm vi phân bố rộng, chủ yếu tấn công tầm gần. Có chi trên đặc trưng một bên, tiềm ẩn một số rủi ro.</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Một Discord nhỏ phổ biến có thể giải phóng một lượng nhỏ năng lượng Havoc để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Một Tacet Discord nhỏ phổ biến có thể giải phóng một lượng nhỏ năng lượng Havoc để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Một Discord nhỏ thông thường có thể giải phóng một lượng nhỏ năng lượng Aero để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Một Tacet Discord nhỏ thông thường có thể giải phóng một lượng nhỏ năng lượng Aero để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Một Discord kích cỡ nhỏ thông thường, có thể giải phóng một lượng nhỏ năng lượng Fusion để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Một Tacet Discord kích cỡ nhỏ thông thường, có thể giải phóng một lượng nhỏ năng lượng Fusion để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Một Discord nhỏ thông thường, có thể giải phóng một lượng nhỏ năng lượng Spectra để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Một Tacet Discord nhỏ thông thường, có thể giải phóng một lượng nhỏ năng lượng Spectra để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Một Sinh Vật Đột Biến đáng gờm nằm sâu trong Rừng Mờ. Thủ lĩnh của bọn Hoochief.</t>
+          <t>Một Sinh Vật Đột Biến đáng gờm nằm sâu trong Dim Forest. Thủ lĩnh của bọn Hoochief.</t>
         </is>
       </c>
     </row>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Choral Calculus Center</t>
+          <t>Trung Tâm Tính Toán Choral</t>
         </is>
       </c>
     </row>
@@ -13836,7 +13836,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -13901,7 +13901,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -14031,7 +14031,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -14291,7 +14291,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Choral Beacon</t>
+          <t>Trạm Phát Sóng Choral</t>
         </is>
       </c>
     </row>
